--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="314">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -268,6 +268,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">fr-resultats-examens-entries:La section contient au moins une entrée Acte (procedure). {entry.where(procedure.exists()).count() &gt;= 1}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -783,111 +787,68 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>Entrées Acte (procedure, 1..*), Références externes (act, 0..*) et Simple observation (observation, 0..*)</t>
+  </si>
+  <si>
+    <t>Section.entry.nullFlavor</t>
+  </si>
+  <si>
+    <t>Section.entry.realmCode</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.displayable</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.root</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.extension</t>
+  </si>
+  <si>
+    <t>Section.entry.templateId</t>
+  </si>
+  <si>
+    <t>Section.entry.typeCode</t>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipEntry|3.0.0</t>
+  </si>
+  <si>
+    <t>Entry.typeCode</t>
+  </si>
+  <si>
+    <t>Section.entry.contextConductionInd</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Entry.contextConductionInd</t>
+  </si>
+  <si>
+    <t>Section.entry.act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-references-externes|0.1.0}
 </t>
   </si>
   <si>
-    <t>Section.entry:frActe</t>
-  </si>
-  <si>
-    <t>frActe</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry.typeCode</t>
-  </si>
-  <si>
-    <t>COMP</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipEntry|3.0.0</t>
-  </si>
-  <si>
-    <t>Entry.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>Entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.act</t>
-  </si>
-  <si>
-    <t>Section.entry.act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act
-</t>
+    <t>Entrée Références externes</t>
   </si>
   <si>
     <t>Entry.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.encounter</t>
   </si>
   <si>
     <t>Section.entry.encounter</t>
@@ -900,20 +861,17 @@
     <t>Entry.encounter</t>
   </si>
   <si>
-    <t>Section.entry:frActe.observation</t>
-  </si>
-  <si>
     <t>Section.entry.observation</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-simple-observation|0.1.0}
 </t>
   </si>
   <si>
+    <t>Entrée Simple observation</t>
+  </si>
+  <si>
     <t>Entry.observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.observationMedia</t>
   </si>
   <si>
     <t>Section.entry.observationMedia</t>
@@ -926,9 +884,6 @@
     <t>Entry.observationMedia</t>
   </si>
   <si>
-    <t>Section.entry:frActe.organizer</t>
-  </si>
-  <si>
     <t>Section.entry.organizer</t>
   </si>
   <si>
@@ -939,9 +894,6 @@
     <t>Entry.organizer</t>
   </si>
   <si>
-    <t>Section.entry:frActe.procedure</t>
-  </si>
-  <si>
     <t>Section.entry.procedure</t>
   </si>
   <si>
@@ -955,9 +907,6 @@
     <t>Entry.procedure</t>
   </si>
   <si>
-    <t>Section.entry:frActe.regionOfInterest</t>
-  </si>
-  <si>
     <t>Section.entry.regionOfInterest</t>
   </si>
   <si>
@@ -968,9 +917,6 @@
     <t>Entry.regionOfInterest</t>
   </si>
   <si>
-    <t>Section.entry:frActe.substanceAdministration</t>
-  </si>
-  <si>
     <t>Section.entry.substanceAdministration</t>
   </si>
   <si>
@@ -981,9 +927,6 @@
     <t>Entry.substanceAdministration</t>
   </si>
   <si>
-    <t>Section.entry:frActe.supply</t>
-  </si>
-  <si>
     <t>Section.entry.supply</t>
   </si>
   <si>
@@ -992,156 +935,6 @@
   </si>
   <si>
     <t>Entry.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes</t>
-  </si>
-  <si>
-    <t>frReferencesExternes</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-references-externes|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Entrée Références externes</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.procedure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Procedure
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation</t>
-  </si>
-  <si>
-    <t>frSimpleObservation</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.observation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-simple-observation|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Entrée Simple observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.procedure</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.supply</t>
   </si>
   <si>
     <t>Section.component</t>
@@ -1514,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK129"/>
+  <dimension ref="A1:AK86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.7578125" customWidth="true" bestFit="true"/>
@@ -1765,25 +1558,25 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>81</v>
@@ -1801,11 +1594,11 @@
         <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1832,11 +1625,11 @@
         <v>75</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>75</v>
@@ -1854,7 +1647,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>81</v>
@@ -1874,10 +1667,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1900,11 +1693,11 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1955,7 +1748,7 @@
         <v>75</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>81</v>
@@ -1975,10 +1768,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2001,11 +1794,11 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2056,7 +1849,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>81</v>
@@ -2068,7 +1861,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
@@ -2076,17 +1869,17 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>81</v>
@@ -2104,11 +1897,11 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2135,11 +1928,11 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2157,7 +1950,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
@@ -2177,17 +1970,17 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>81</v>
@@ -2205,11 +1998,11 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2260,7 +2053,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>81</v>
@@ -2280,17 +2073,17 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>81</v>
@@ -2308,11 +2101,11 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2363,7 +2156,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -2383,17 +2176,17 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>76</v>
@@ -2411,11 +2204,11 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2424,7 +2217,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>75</v>
@@ -2466,7 +2259,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -2486,17 +2279,17 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>76</v>
@@ -2514,11 +2307,11 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2569,7 +2362,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -2589,10 +2382,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2600,10 +2393,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2615,11 +2408,11 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2658,17 +2451,17 @@
         <v>75</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2688,13 +2481,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
@@ -2716,13 +2509,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2773,7 +2566,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -2793,17 +2586,17 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>81</v>
@@ -2821,11 +2614,11 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2852,11 +2645,11 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2874,7 +2667,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -2894,17 +2687,17 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>81</v>
@@ -2922,11 +2715,11 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2977,7 +2770,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -2997,17 +2790,17 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>81</v>
@@ -3025,11 +2818,11 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3080,7 +2873,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3100,17 +2893,17 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>76</v>
@@ -3128,11 +2921,11 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3144,7 +2937,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -3183,7 +2976,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3203,17 +2996,17 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>81</v>
@@ -3231,11 +3024,11 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3286,7 +3079,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3306,13 +3099,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -3334,13 +3127,13 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3391,7 +3184,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3411,17 +3204,17 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>81</v>
@@ -3439,11 +3232,11 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3470,11 +3263,11 @@
         <v>75</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>75</v>
@@ -3492,7 +3285,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3512,17 +3305,17 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>81</v>
@@ -3540,11 +3333,11 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3595,7 +3388,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3615,17 +3408,17 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>81</v>
@@ -3643,11 +3436,11 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3698,7 +3491,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3718,17 +3511,17 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>76</v>
@@ -3746,11 +3539,11 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3762,7 +3555,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -3801,7 +3594,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -3821,17 +3614,17 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>81</v>
@@ -3849,11 +3642,11 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3904,7 +3697,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -3924,13 +3717,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3952,13 +3745,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4009,7 +3802,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4029,17 +3822,17 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>81</v>
@@ -4057,11 +3850,11 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4088,11 +3881,11 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4110,7 +3903,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4130,17 +3923,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>81</v>
@@ -4158,11 +3951,11 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4213,7 +4006,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4233,17 +4026,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>81</v>
@@ -4261,11 +4054,11 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4316,7 +4109,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4336,17 +4129,17 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>76</v>
@@ -4364,11 +4157,11 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4380,7 +4173,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4419,7 +4212,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4439,17 +4232,17 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>81</v>
@@ -4467,11 +4260,11 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4522,7 +4315,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4542,10 +4335,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4568,10 +4361,10 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4623,7 +4416,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4643,10 +4436,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4669,7 +4462,7 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -4680,7 +4473,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>75</v>
@@ -4698,11 +4491,11 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -4720,7 +4513,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4740,10 +4533,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4766,7 +4559,7 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -4777,7 +4570,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>75</v>
@@ -4795,11 +4588,11 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -4817,7 +4610,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -4837,10 +4630,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4854,7 +4647,7 @@
         <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>
@@ -4863,13 +4656,13 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4920,7 +4713,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4940,10 +4733,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4957,7 +4750,7 @@
         <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>75</v>
@@ -4966,13 +4759,13 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5023,7 +4816,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5043,17 +4836,17 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>81</v>
@@ -5071,11 +4864,11 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5102,11 +4895,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5124,7 +4917,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5144,10 +4937,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5163,7 +4956,7 @@
         <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -5172,11 +4965,11 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5188,7 +4981,7 @@
         <v>75</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>75</v>
@@ -5227,7 +5020,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5247,17 +5040,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>76</v>
@@ -5266,7 +5059,7 @@
         <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>75</v>
@@ -5275,11 +5068,11 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5291,7 +5084,7 @@
         <v>75</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>75</v>
@@ -5330,7 +5123,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5350,17 +5143,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>81</v>
@@ -5378,11 +5171,11 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5394,7 +5187,7 @@
         <v>75</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>75</v>
@@ -5433,7 +5226,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5453,17 +5246,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
@@ -5481,11 +5274,11 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5536,7 +5329,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5556,17 +5349,17 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>76</v>
@@ -5575,7 +5368,7 @@
         <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>75</v>
@@ -5584,11 +5377,11 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5600,7 +5393,7 @@
         <v>75</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>75</v>
@@ -5639,7 +5432,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5659,10 +5452,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5685,11 +5478,11 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5740,7 +5533,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5760,10 +5553,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5786,11 +5579,11 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5841,7 +5634,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -5861,17 +5654,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>81</v>
@@ -5889,11 +5682,11 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5944,7 +5737,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -5964,17 +5757,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -5992,11 +5785,11 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6047,7 +5840,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6067,17 +5860,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -6095,11 +5888,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6150,7 +5943,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6170,10 +5963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6187,7 +5980,7 @@
         <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -6196,17 +5989,17 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6255,7 +6048,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6275,10 +6068,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6292,7 +6085,7 @@
         <v>76</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>75</v>
@@ -6301,16 +6094,16 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6360,7 +6153,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6380,10 +6173,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6406,15 +6199,15 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6463,7 +6256,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6483,10 +6276,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6509,15 +6302,15 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6542,11 +6335,11 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -6564,7 +6357,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6584,10 +6377,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6610,17 +6403,17 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6669,7 +6462,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6689,10 +6482,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6715,13 +6508,13 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -6770,7 +6563,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6790,10 +6583,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6816,13 +6609,13 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -6871,7 +6664,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6889,12 +6682,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6908,7 +6701,7 @@
         <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
@@ -6917,9 +6710,11 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L53" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6958,17 +6753,19 @@
         <v>75</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6988,23 +6785,23 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C54" t="s" s="2">
         <v>250</v>
       </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F54" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7016,10 +6813,12 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7045,13 +6844,11 @@
         <v>75</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>75</v>
@@ -7069,13 +6866,13 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>246</v>
+        <v>91</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
@@ -7092,20 +6889,18 @@
         <v>251</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E55" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7117,11 +6912,11 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7148,11 +6943,13 @@
         <v>75</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -7170,13 +6967,13 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>75</v>
@@ -7190,10 +6987,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7204,7 +7001,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7216,11 +7013,11 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7271,19 +7068,19 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -7291,16 +7088,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
@@ -7317,11 +7116,11 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7348,13 +7147,11 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7372,7 +7169,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7384,7 +7181,7 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -7392,17 +7189,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>81</v>
@@ -7420,11 +7217,11 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7451,11 +7248,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -7473,7 +7272,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7493,17 +7292,17 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>81</v>
@@ -7521,11 +7320,11 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7576,7 +7375,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7596,20 +7395,20 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>76</v>
@@ -7624,11 +7423,11 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7637,7 +7436,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>75</v>
@@ -7679,7 +7478,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7699,17 +7498,17 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>76</v>
@@ -7727,11 +7526,11 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7740,7 +7539,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>75</v>
@@ -7782,7 +7581,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7802,23 +7601,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -7830,11 +7627,11 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7885,13 +7682,13 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>75</v>
@@ -7905,10 +7702,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7919,7 +7716,7 @@
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
@@ -7931,16 +7728,14 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
@@ -7962,13 +7757,11 @@
         <v>75</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -7986,13 +7779,13 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>126</v>
+        <v>262</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>75</v>
@@ -8006,10 +7799,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8032,18 +7825,18 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>75</v>
@@ -8061,11 +7854,13 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
@@ -8083,7 +7878,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8103,10 +7898,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8129,9 +7924,11 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L65" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8140,7 +7937,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>75</v>
@@ -8182,7 +7979,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8202,10 +7999,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8228,7 +8025,7 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8281,7 +8078,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8301,10 +8098,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8327,9 +8124,11 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L67" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8380,7 +8179,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8400,10 +8199,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8426,7 +8225,7 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8479,7 +8278,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8499,10 +8298,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8525,7 +8324,7 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8578,7 +8377,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8598,10 +8397,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8624,9 +8423,11 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L70" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8677,7 +8478,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8697,10 +8498,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8723,11 +8524,9 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8778,7 +8577,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -8798,10 +8597,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8824,7 +8623,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8877,7 +8676,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -8897,10 +8696,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8923,7 +8722,7 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8976,7 +8775,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -8996,10 +8795,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9010,7 +8809,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>75</v>
@@ -9022,12 +8821,16 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -9075,13 +8878,13 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>75</v>
@@ -9095,23 +8898,23 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
@@ -9123,10 +8926,12 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9152,13 +8957,11 @@
         <v>75</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>75</v>
@@ -9176,13 +8979,13 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>246</v>
+        <v>91</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>75</v>
@@ -9196,23 +8999,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>252</v>
+        <v>301</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E76" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>75</v>
@@ -9224,11 +9025,11 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9255,11 +9056,13 @@
         <v>75</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -9277,13 +9080,13 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>75</v>
@@ -9297,10 +9100,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9311,7 +9114,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>75</v>
@@ -9323,11 +9126,11 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9378,19 +9181,19 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -9398,16 +9201,18 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F78" t="s" s="2">
         <v>81</v>
       </c>
@@ -9424,11 +9229,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9455,13 +9260,11 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -9479,7 +9282,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9491,7 +9294,7 @@
         <v>75</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>75</v>
@@ -9499,17 +9302,17 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>81</v>
@@ -9527,11 +9330,11 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9558,11 +9361,13 @@
         <v>75</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -9580,7 +9385,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9600,17 +9405,17 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
@@ -9628,11 +9433,11 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9683,7 +9488,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9703,20 +9508,20 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>76</v>
@@ -9731,11 +9536,11 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9744,7 +9549,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -9786,7 +9591,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -9806,17 +9611,17 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>264</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>76</v>
@@ -9834,11 +9639,11 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9847,7 +9652,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>75</v>
@@ -9889,7 +9694,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -9909,23 +9714,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E83" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>75</v>
@@ -9937,11 +9740,11 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9992,13 +9795,13 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>75</v>
@@ -10012,10 +9815,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10026,7 +9829,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>75</v>
@@ -10038,11 +9841,11 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>123</v>
+        <v>310</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10051,7 +9854,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>75</v>
@@ -10093,13 +9896,13 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>126</v>
+        <v>309</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>75</v>
@@ -10113,10 +9916,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10139,18 +9942,18 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>75</v>
@@ -10168,11 +9971,13 @@
         <v>75</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -10190,7 +9995,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10210,10 +10015,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10221,7 +10026,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>76</v>
@@ -10236,7 +10041,7 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>108</v>
+        <v>313</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10247,7 +10052,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>75</v>
@@ -10289,10 +10094,10 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -10307,4327 +10112,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L97" s="2"/>
-      <c r="M97" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y97" s="2"/>
-      <c r="Z97" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L98" s="2"/>
-      <c r="M98" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L99" s="2"/>
-      <c r="M99" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E100" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L100" s="2"/>
-      <c r="M100" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y100" s="2"/>
-      <c r="Z100" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E101" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L101" s="2"/>
-      <c r="M101" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E102" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L102" s="2"/>
-      <c r="M102" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E103" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L103" s="2"/>
-      <c r="M103" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L104" s="2"/>
-      <c r="M104" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L105" s="2"/>
-      <c r="M105" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y106" s="2"/>
-      <c r="Z106" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L107" s="2"/>
-      <c r="M107" s="2"/>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M110" s="2"/>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L112" s="2"/>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L115" s="2"/>
-      <c r="M115" s="2"/>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L116" s="2"/>
-      <c r="M116" s="2"/>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
-      <c r="O117" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L118" s="2"/>
-      <c r="M118" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y118" s="2"/>
-      <c r="Z118" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L120" s="2"/>
-      <c r="M120" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L121" s="2"/>
-      <c r="M121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y121" s="2"/>
-      <c r="Z121" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E122" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L122" s="2"/>
-      <c r="M122" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E123" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L123" s="2"/>
-      <c r="M123" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L124" s="2"/>
-      <c r="M124" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E125" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L125" s="2"/>
-      <c r="M125" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L126" s="2"/>
-      <c r="M126" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L127" s="2"/>
-      <c r="M127" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK129">
+  <autoFilter ref="A1:AK86">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14637,7 +10123,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI128">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
